--- a/examples/06_SiNx_on_fused_silica_65deg.xlsx
+++ b/examples/06_SiNx_on_fused_silica_65deg.xlsx
@@ -3901,7 +3901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -3971,100 +3971,112 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Угол падения, град</t>
+          <t>Задняя сторона подложки</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>65</v>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>нет (зачернена / матирована / отсечена)</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Толщина (номинал), нм</t>
+          <t>Угол падения, град</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>700</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
+          <t>Толщина (номинал), нм</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
           <t>Неопределённость толщины, %</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>±6</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>Диапазон длин волн, нм</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>400 – 800, шаг 2</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>Спектральная полоса прибора, нм (FWHM)</t>
         </is>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B11" s="4" t="n">
         <v>1.1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Шумовая модель</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>столбцы σΨ, σΔ — повторяемость прибора (σΔ растёт при Ψ → 0)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Прибор</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>RCE-эллипсометр с ПЗС, все длины волн одновременно; Δ в диапазоне 0–360°; конвенция N = n − ik (Аззам–Башара)</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Возможные дефекты</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>неоднородность по глубине (линейный градиент n), шероховатость поверхности (EMA-слой Бруггемана 50/50), поглощение (хвост ниже края: второй осциллятор Тауца–Лоренца с теми же E0, C и порогом E_t = 1.2 эВ; размер — k хвоста при 400 нм)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Назначение</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>тестовый файл для приложения: опорный фит однородной плёнки → ИИ по остатку → окончательный фит; истинные параметры — в answer_key.xlsx</t>
         </is>

--- a/examples/06_SiNx_on_fused_silica_65deg.xlsx
+++ b/examples/06_SiNx_on_fused_silica_65deg.xlsx
@@ -478,10 +478,10 @@
         <v>400</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>6.6689</v>
+        <v>6.6698</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>150.0841</v>
+        <v>150.0961</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0.035</v>
@@ -495,10 +495,10 @@
         <v>402</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>6.8596</v>
+        <v>6.8603</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>160.3321</v>
+        <v>160.3398</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>0.0347</v>
@@ -512,16 +512,16 @@
         <v>404</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>6.9784</v>
+        <v>6.9789</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>169.7268</v>
+        <v>169.7301</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>0.0344</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.3136</v>
+        <v>0.3135</v>
       </c>
     </row>
     <row r="5">
@@ -529,10 +529,10 @@
         <v>406</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>6.9616</v>
+        <v>6.9621</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>179.4023</v>
+        <v>179.4008</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>0.0341</v>
@@ -546,16 +546,16 @@
         <v>408</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>6.8722</v>
+        <v>6.8727</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>189.4169</v>
+        <v>189.4104</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>0.0337</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.3111</v>
+        <v>0.311</v>
       </c>
     </row>
     <row r="7">
@@ -563,10 +563,10 @@
         <v>410</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6.7952</v>
+        <v>6.7957</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>198.4664</v>
+        <v>198.4538</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>0.0334</v>
@@ -580,10 +580,10 @@
         <v>412</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>6.5095</v>
+        <v>6.5102</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>210.1647</v>
+        <v>210.1448</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>0.0331</v>
@@ -597,16 +597,16 @@
         <v>414</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>6.2715</v>
+        <v>6.2724</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>221.8807</v>
+        <v>221.8515</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>0.0328</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.3344</v>
+        <v>0.3343</v>
       </c>
     </row>
     <row r="10">
@@ -614,16 +614,16 @@
         <v>416</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>5.9429</v>
+        <v>5.9439</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>235.3967</v>
+        <v>235.3553</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>0.0325</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.349</v>
+        <v>0.3489</v>
       </c>
     </row>
     <row r="11">
@@ -631,10 +631,10 @@
         <v>418</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>5.6057</v>
+        <v>5.6067</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>249.3718</v>
+        <v>249.3156</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0.0322</v>
@@ -648,16 +648,16 @@
         <v>420</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>5.292</v>
+        <v>5.2928</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>266.7244</v>
+        <v>266.6507</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0.0319</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.385</v>
+        <v>0.3849</v>
       </c>
     </row>
     <row r="13">
@@ -665,16 +665,16 @@
         <v>422</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>5.0027</v>
+        <v>5.0029</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>285.6202</v>
+        <v>285.5313</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0.0316</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.4011</v>
+        <v>0.401</v>
       </c>
     </row>
     <row r="14">
@@ -682,10 +682,10 @@
         <v>424</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>4.8918</v>
+        <v>4.8911</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>307.9252</v>
+        <v>307.8321</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>0.0313</v>
@@ -699,16 +699,16 @@
         <v>426</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>4.9075</v>
+        <v>4.9061</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>331.1099</v>
+        <v>331.0344</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>0.0311</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.4017</v>
+        <v>0.4018</v>
       </c>
     </row>
     <row r="16">
@@ -716,16 +716,16 @@
         <v>428</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>5.1418</v>
+        <v>5.1405</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>355.8407</v>
+        <v>355.8054</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>0.0308</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.38</v>
+        <v>0.3801</v>
       </c>
     </row>
     <row r="17">
@@ -733,10 +733,10 @@
         <v>430</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>5.5568</v>
+        <v>5.5566</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>19.2482</v>
+        <v>19.26</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>0.0305</v>
@@ -750,10 +750,10 @@
         <v>432</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>5.9964</v>
+        <v>5.9974</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>40.6783</v>
+        <v>40.7261</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>0.0302</v>
@@ -767,16 +767,16 @@
         <v>434</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>6.4859</v>
+        <v>6.4876</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>59.3941</v>
+        <v>59.4584</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>0.0299</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.2945</v>
+        <v>0.2944</v>
       </c>
     </row>
     <row r="20">
@@ -784,10 +784,10 @@
         <v>436</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>6.9285</v>
+        <v>6.9304</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>75.5202</v>
+        <v>75.58580000000001</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>0.0297</v>
@@ -801,16 +801,16 @@
         <v>438</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>7.344</v>
+        <v>7.3457</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>90.24630000000001</v>
+        <v>90.3044</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>0.0294</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.2572</v>
+        <v>0.2571</v>
       </c>
     </row>
     <row r="22">
@@ -818,16 +818,16 @@
         <v>440</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>7.6198</v>
+        <v>7.6212</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>102.8604</v>
+        <v>102.9083</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>0.0291</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.2439</v>
+        <v>0.2438</v>
       </c>
     </row>
     <row r="23">
@@ -835,16 +835,16 @@
         <v>442</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>7.8768</v>
+        <v>7.8779</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>113.6126</v>
+        <v>113.6508</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>0.0288</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.233</v>
+        <v>0.2329</v>
       </c>
     </row>
     <row r="24">
@@ -852,10 +852,10 @@
         <v>444</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>8.1486</v>
+        <v>8.1495</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>124.4715</v>
+        <v>124.501</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>0.0286</v>
@@ -869,10 +869,10 @@
         <v>446</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>8.3758</v>
+        <v>8.3764</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>134.4602</v>
+        <v>134.4826</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>0.0283</v>
@@ -886,10 +886,10 @@
         <v>448</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>8.5054</v>
+        <v>8.505800000000001</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>143.6351</v>
+        <v>143.6516</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>0.0281</v>
@@ -903,10 +903,10 @@
         <v>450</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>8.6623</v>
+        <v>8.662599999999999</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>152.5378</v>
+        <v>152.5496</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>0.0278</v>
@@ -920,10 +920,10 @@
         <v>452</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>8.803699999999999</v>
+        <v>8.804</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>161.7206</v>
+        <v>161.7282</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>0.0275</v>
@@ -937,10 +937,10 @@
         <v>454</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>8.8742</v>
+        <v>8.8744</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>170.2545</v>
+        <v>170.2585</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>0.0273</v>
@@ -954,10 +954,10 @@
         <v>456</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>8.850899999999999</v>
+        <v>8.851100000000001</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>178.8231</v>
+        <v>178.8237</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>0.027</v>
@@ -971,10 +971,10 @@
         <v>458</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>8.8827</v>
+        <v>8.8828</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>187.3188</v>
+        <v>187.316</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>0.0268</v>
@@ -988,10 +988,10 @@
         <v>460</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>8.8726</v>
+        <v>8.8727</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>196.2781</v>
+        <v>196.2719</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>0.0266</v>
@@ -1005,10 +1005,10 @@
         <v>462</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>8.8302</v>
+        <v>8.830299999999999</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>205.3589</v>
+        <v>205.3488</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>0.0263</v>
@@ -1022,10 +1022,10 @@
         <v>464</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>8.757300000000001</v>
+        <v>8.757400000000001</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>214.2989</v>
+        <v>214.2844</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>0.0261</v>
@@ -1042,7 +1042,7 @@
         <v>8.7736</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>223.4074</v>
+        <v>223.3878</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>0.0258</v>
@@ -1059,7 +1059,7 @@
         <v>8.709</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>233.469</v>
+        <v>233.4432</v>
       </c>
       <c r="D36" s="2" t="n">
         <v>0.0256</v>
@@ -1073,10 +1073,10 @@
         <v>470</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>8.764699999999999</v>
+        <v>8.7645</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>243.4602</v>
+        <v>243.4272</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>0.0254</v>
@@ -1090,16 +1090,16 @@
         <v>472</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>8.814500000000001</v>
+        <v>8.814</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>253.3576</v>
+        <v>253.3156</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>0.0251</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.1842</v>
+        <v>0.1843</v>
       </c>
     </row>
     <row r="39">
@@ -1107,16 +1107,16 @@
         <v>474</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>8.8223</v>
+        <v>8.8215</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>264.5442</v>
+        <v>264.4919</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>0.0249</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.1809</v>
+        <v>0.181</v>
       </c>
     </row>
     <row r="40">
@@ -1124,10 +1124,10 @@
         <v>476</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>8.983499999999999</v>
+        <v>8.982200000000001</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>276.3865</v>
+        <v>276.3229</v>
       </c>
       <c r="D40" s="2" t="n">
         <v>0.0247</v>
@@ -1141,16 +1141,16 @@
         <v>478</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>9.222200000000001</v>
+        <v>9.2204</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>288.9665</v>
+        <v>288.8918</v>
       </c>
       <c r="D41" s="2" t="n">
         <v>0.0245</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.1706</v>
+        <v>0.1707</v>
       </c>
     </row>
     <row r="42">
@@ -1158,16 +1158,16 @@
         <v>480</v>
       </c>
       <c r="B42" s="2" t="n">
-        <v>9.5123</v>
+        <v>9.5101</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>302.3022</v>
+        <v>302.2196</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>0.0242</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.1638</v>
+        <v>0.1639</v>
       </c>
     </row>
     <row r="43">
@@ -1175,10 +1175,10 @@
         <v>482</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>9.8718</v>
+        <v>9.8697</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>316.4356</v>
+        <v>316.3529</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>0.024</v>
@@ -1192,16 +1192,16 @@
         <v>484</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>10.2583</v>
+        <v>10.257</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>331.7848</v>
+        <v>331.7157</v>
       </c>
       <c r="D44" s="2" t="n">
         <v>0.0238</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.1494</v>
+        <v>0.1495</v>
       </c>
     </row>
     <row r="45">
@@ -1209,10 +1209,10 @@
         <v>486</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>10.6174</v>
+        <v>10.6173</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>347.8279</v>
+        <v>347.7885</v>
       </c>
       <c r="D45" s="2" t="n">
         <v>0.0236</v>
@@ -1226,10 +1226,10 @@
         <v>488</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>10.7867</v>
+        <v>10.7875</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>3.6864</v>
+        <v>3.6875</v>
       </c>
       <c r="D46" s="2" t="n">
         <v>0.0234</v>
@@ -1243,10 +1243,10 @@
         <v>490</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>10.9058</v>
+        <v>10.9065</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>19.6168</v>
+        <v>19.6561</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>0.0232</v>
@@ -1263,7 +1263,7 @@
         <v>10.8922</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>34.7401</v>
+        <v>34.8042</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>0.023</v>
@@ -1277,10 +1277,10 @@
         <v>494</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>10.6498</v>
+        <v>10.6491</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>48.7462</v>
+        <v>48.8192</v>
       </c>
       <c r="D49" s="2" t="n">
         <v>0.0228</v>
@@ -1294,10 +1294,10 @@
         <v>496</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>10.5335</v>
+        <v>10.5324</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>61.5521</v>
+        <v>61.6223</v>
       </c>
       <c r="D50" s="2" t="n">
         <v>0.0226</v>
@@ -1311,10 +1311,10 @@
         <v>498</v>
       </c>
       <c r="B51" s="2" t="n">
-        <v>10.3539</v>
+        <v>10.3528</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>72.8361</v>
+        <v>72.898</v>
       </c>
       <c r="D51" s="2" t="n">
         <v>0.0224</v>
@@ -1328,10 +1328,10 @@
         <v>500</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>10.2126</v>
+        <v>10.2118</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>83.05159999999999</v>
+        <v>83.10339999999999</v>
       </c>
       <c r="D52" s="2" t="n">
         <v>0.0222</v>
@@ -1345,10 +1345,10 @@
         <v>502</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>10.035</v>
+        <v>10.0344</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>92.8548</v>
+        <v>92.8972</v>
       </c>
       <c r="D53" s="2" t="n">
         <v>0.022</v>
@@ -1362,10 +1362,10 @@
         <v>504</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>9.963100000000001</v>
+        <v>9.9627</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>101.63</v>
+        <v>101.6642</v>
       </c>
       <c r="D54" s="2" t="n">
         <v>0.0218</v>
@@ -1379,10 +1379,10 @@
         <v>506</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>9.948700000000001</v>
+        <v>9.948499999999999</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>110.2298</v>
+        <v>110.2572</v>
       </c>
       <c r="D55" s="2" t="n">
         <v>0.0216</v>
@@ -1396,10 +1396,10 @@
         <v>508</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>9.886699999999999</v>
+        <v>9.8866</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>118.367</v>
+        <v>118.389</v>
       </c>
       <c r="D56" s="2" t="n">
         <v>0.0215</v>
@@ -1413,10 +1413,10 @@
         <v>510</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>9.9237</v>
+        <v>9.9236</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>126.1262</v>
+        <v>126.1436</v>
       </c>
       <c r="D57" s="2" t="n">
         <v>0.0213</v>
@@ -1430,10 +1430,10 @@
         <v>512</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>9.8911</v>
+        <v>9.891</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>133.6765</v>
+        <v>133.6904</v>
       </c>
       <c r="D58" s="2" t="n">
         <v>0.0211</v>
@@ -1450,7 +1450,7 @@
         <v>9.9069</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>140.8131</v>
+        <v>140.824</v>
       </c>
       <c r="D59" s="2" t="n">
         <v>0.0209</v>
@@ -1467,7 +1467,7 @@
         <v>9.960800000000001</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>147.9826</v>
+        <v>147.991</v>
       </c>
       <c r="D60" s="2" t="n">
         <v>0.0207</v>
@@ -1484,7 +1484,7 @@
         <v>9.9213</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>154.6587</v>
+        <v>154.665</v>
       </c>
       <c r="D61" s="2" t="n">
         <v>0.0206</v>
@@ -1501,7 +1501,7 @@
         <v>9.9152</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>161.6817</v>
+        <v>161.6861</v>
       </c>
       <c r="D62" s="2" t="n">
         <v>0.0204</v>
@@ -1515,10 +1515,10 @@
         <v>522</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>9.9398</v>
+        <v>9.9399</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>168.7971</v>
+        <v>168.7999</v>
       </c>
       <c r="D63" s="2" t="n">
         <v>0.0202</v>
@@ -1535,7 +1535,7 @@
         <v>9.9328</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>175.4113</v>
+        <v>175.4126</v>
       </c>
       <c r="D64" s="2" t="n">
         <v>0.0201</v>
@@ -1552,7 +1552,7 @@
         <v>9.9366</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>181.7976</v>
+        <v>181.7975</v>
       </c>
       <c r="D65" s="2" t="n">
         <v>0.0199</v>
@@ -1569,7 +1569,7 @@
         <v>9.9391</v>
       </c>
       <c r="C66" s="2" t="n">
-        <v>188.6268</v>
+        <v>188.6253</v>
       </c>
       <c r="D66" s="2" t="n">
         <v>0.0198</v>
@@ -1586,7 +1586,7 @@
         <v>9.952199999999999</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>195.1161</v>
+        <v>195.1132</v>
       </c>
       <c r="D67" s="2" t="n">
         <v>0.0196</v>
@@ -1600,10 +1600,10 @@
         <v>532</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>9.941700000000001</v>
+        <v>9.941599999999999</v>
       </c>
       <c r="C68" s="2" t="n">
-        <v>201.628</v>
+        <v>201.6237</v>
       </c>
       <c r="D68" s="2" t="n">
         <v>0.0195</v>
@@ -1617,10 +1617,10 @@
         <v>534</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>9.9633</v>
+        <v>9.963200000000001</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>208.1392</v>
+        <v>208.1334</v>
       </c>
       <c r="D69" s="2" t="n">
         <v>0.0193</v>
@@ -1634,10 +1634,10 @@
         <v>536</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>9.9724</v>
+        <v>9.972300000000001</v>
       </c>
       <c r="C70" s="2" t="n">
-        <v>215.0494</v>
+        <v>215.042</v>
       </c>
       <c r="D70" s="2" t="n">
         <v>0.0192</v>
@@ -1651,10 +1651,10 @@
         <v>538</v>
       </c>
       <c r="B71" s="2" t="n">
-        <v>9.967700000000001</v>
+        <v>9.967599999999999</v>
       </c>
       <c r="C71" s="2" t="n">
-        <v>221.5287</v>
+        <v>221.5195</v>
       </c>
       <c r="D71" s="2" t="n">
         <v>0.019</v>
@@ -1668,10 +1668,10 @@
         <v>540</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>10.0447</v>
+        <v>10.0446</v>
       </c>
       <c r="C72" s="2" t="n">
-        <v>228.3602</v>
+        <v>228.3491</v>
       </c>
       <c r="D72" s="2" t="n">
         <v>0.0189</v>
@@ -1685,10 +1685,10 @@
         <v>542</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>10.0944</v>
+        <v>10.0941</v>
       </c>
       <c r="C73" s="2" t="n">
-        <v>234.8908</v>
+        <v>234.8774</v>
       </c>
       <c r="D73" s="2" t="n">
         <v>0.0187</v>
@@ -1702,10 +1702,10 @@
         <v>544</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>10.1457</v>
+        <v>10.1453</v>
       </c>
       <c r="C74" s="2" t="n">
-        <v>242.0305</v>
+        <v>242.0146</v>
       </c>
       <c r="D74" s="2" t="n">
         <v>0.0186</v>
@@ -1719,10 +1719,10 @@
         <v>546</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>10.2391</v>
+        <v>10.2386</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>248.9893</v>
+        <v>248.9706</v>
       </c>
       <c r="D75" s="2" t="n">
         <v>0.0185</v>
@@ -1736,10 +1736,10 @@
         <v>548</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>10.404</v>
+        <v>10.4033</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>255.877</v>
+        <v>255.8549</v>
       </c>
       <c r="D76" s="2" t="n">
         <v>0.0183</v>
@@ -1753,16 +1753,16 @@
         <v>550</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>10.5674</v>
+        <v>10.5665</v>
       </c>
       <c r="C77" s="2" t="n">
-        <v>263.1891</v>
+        <v>263.1633</v>
       </c>
       <c r="D77" s="2" t="n">
         <v>0.0182</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>0.111</v>
+        <v>0.1111</v>
       </c>
     </row>
     <row r="78">
@@ -1770,10 +1770,10 @@
         <v>552</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>10.8349</v>
+        <v>10.8337</v>
       </c>
       <c r="C78" s="2" t="n">
-        <v>270.6683</v>
+        <v>270.6383</v>
       </c>
       <c r="D78" s="2" t="n">
         <v>0.0181</v>
@@ -1787,10 +1787,10 @@
         <v>554</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>11.0606</v>
+        <v>11.059</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>278.2349</v>
+        <v>278.2003</v>
       </c>
       <c r="D79" s="2" t="n">
         <v>0.0179</v>
@@ -1804,10 +1804,10 @@
         <v>556</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>11.419</v>
+        <v>11.4171</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>286.1439</v>
+        <v>286.1044</v>
       </c>
       <c r="D80" s="2" t="n">
         <v>0.0178</v>
@@ -1821,16 +1821,16 @@
         <v>558</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>11.8116</v>
+        <v>11.8094</v>
       </c>
       <c r="C81" s="2" t="n">
-        <v>294.4611</v>
+        <v>294.4169</v>
       </c>
       <c r="D81" s="2" t="n">
         <v>0.0177</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>0.0973</v>
+        <v>0.0974</v>
       </c>
     </row>
     <row r="82">
@@ -1838,10 +1838,10 @@
         <v>560</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>12.2601</v>
+        <v>12.2577</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>303.0195</v>
+        <v>302.9713</v>
       </c>
       <c r="D82" s="2" t="n">
         <v>0.0176</v>
@@ -1855,10 +1855,10 @@
         <v>562</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>12.7179</v>
+        <v>12.7156</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>312.4682</v>
+        <v>312.4183</v>
       </c>
       <c r="D83" s="2" t="n">
         <v>0.0175</v>
@@ -1872,10 +1872,10 @@
         <v>564</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>13.2</v>
+        <v>13.1982</v>
       </c>
       <c r="C84" s="2" t="n">
-        <v>322.393</v>
+        <v>322.3449</v>
       </c>
       <c r="D84" s="2" t="n">
         <v>0.0174</v>
@@ -1889,10 +1889,10 @@
         <v>566</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>13.6218</v>
+        <v>13.6209</v>
       </c>
       <c r="C85" s="2" t="n">
-        <v>332.5256</v>
+        <v>332.4847</v>
       </c>
       <c r="D85" s="2" t="n">
         <v>0.0173</v>
@@ -1906,10 +1906,10 @@
         <v>568</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>13.9385</v>
+        <v>13.9386</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>343.3899</v>
+        <v>343.3623</v>
       </c>
       <c r="D86" s="2" t="n">
         <v>0.0172</v>
@@ -1923,10 +1923,10 @@
         <v>570</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>14.1767</v>
+        <v>14.1774</v>
       </c>
       <c r="C87" s="2" t="n">
-        <v>354.6435</v>
+        <v>354.6337</v>
       </c>
       <c r="D87" s="2" t="n">
         <v>0.017</v>
@@ -1940,10 +1940,10 @@
         <v>572</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>14.1833</v>
+        <v>14.1841</v>
       </c>
       <c r="C88" s="2" t="n">
-        <v>5.6371</v>
+        <v>5.6464</v>
       </c>
       <c r="D88" s="2" t="n">
         <v>0.0169</v>
@@ -1957,10 +1957,10 @@
         <v>574</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>14.0112</v>
+        <v>14.0114</v>
       </c>
       <c r="C89" s="2" t="n">
-        <v>16.5569</v>
+        <v>16.5827</v>
       </c>
       <c r="D89" s="2" t="n">
         <v>0.0168</v>
@@ -1974,10 +1974,10 @@
         <v>576</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>13.7408</v>
+        <v>13.7402</v>
       </c>
       <c r="C90" s="2" t="n">
-        <v>27.0473</v>
+        <v>27.084</v>
       </c>
       <c r="D90" s="2" t="n">
         <v>0.0168</v>
@@ -1991,10 +1991,10 @@
         <v>578</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>13.353</v>
+        <v>13.3516</v>
       </c>
       <c r="C91" s="2" t="n">
-        <v>36.9803</v>
+        <v>37.0223</v>
       </c>
       <c r="D91" s="2" t="n">
         <v>0.0167</v>
@@ -2008,10 +2008,10 @@
         <v>580</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>12.9275</v>
+        <v>12.9256</v>
       </c>
       <c r="C92" s="2" t="n">
-        <v>45.9034</v>
+        <v>45.9459</v>
       </c>
       <c r="D92" s="2" t="n">
         <v>0.0166</v>
@@ -2025,10 +2025,10 @@
         <v>582</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>12.4974</v>
+        <v>12.4954</v>
       </c>
       <c r="C93" s="2" t="n">
-        <v>54.4082</v>
+        <v>54.4483</v>
       </c>
       <c r="D93" s="2" t="n">
         <v>0.0165</v>
@@ -2042,10 +2042,10 @@
         <v>584</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>12.1007</v>
+        <v>12.0988</v>
       </c>
       <c r="C94" s="2" t="n">
-        <v>62.246</v>
+        <v>62.2823</v>
       </c>
       <c r="D94" s="2" t="n">
         <v>0.0164</v>
@@ -2059,10 +2059,10 @@
         <v>586</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>11.7257</v>
+        <v>11.724</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>69.4864</v>
+        <v>69.5185</v>
       </c>
       <c r="D95" s="2" t="n">
         <v>0.0163</v>
@@ -2076,10 +2076,10 @@
         <v>588</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>11.3875</v>
+        <v>11.3861</v>
       </c>
       <c r="C96" s="2" t="n">
-        <v>76.7854</v>
+        <v>76.8134</v>
       </c>
       <c r="D96" s="2" t="n">
         <v>0.0162</v>
@@ -2093,10 +2093,10 @@
         <v>590</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>11.0743</v>
+        <v>11.0731</v>
       </c>
       <c r="C97" s="2" t="n">
-        <v>83.1802</v>
+        <v>83.20440000000001</v>
       </c>
       <c r="D97" s="2" t="n">
         <v>0.0162</v>
@@ -2110,10 +2110,10 @@
         <v>592</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>10.8527</v>
+        <v>10.8518</v>
       </c>
       <c r="C98" s="2" t="n">
-        <v>89.1906</v>
+        <v>89.21129999999999</v>
       </c>
       <c r="D98" s="2" t="n">
         <v>0.0161</v>
@@ -2127,10 +2127,10 @@
         <v>594</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>10.6556</v>
+        <v>10.6549</v>
       </c>
       <c r="C99" s="2" t="n">
-        <v>95.34739999999999</v>
+        <v>95.3653</v>
       </c>
       <c r="D99" s="2" t="n">
         <v>0.016</v>
@@ -2144,10 +2144,10 @@
         <v>596</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>10.4396</v>
+        <v>10.439</v>
       </c>
       <c r="C100" s="2" t="n">
-        <v>100.9674</v>
+        <v>100.9826</v>
       </c>
       <c r="D100" s="2" t="n">
         <v>0.0159</v>
@@ -2161,10 +2161,10 @@
         <v>598</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>10.3053</v>
+        <v>10.3049</v>
       </c>
       <c r="C101" s="2" t="n">
-        <v>106.6147</v>
+        <v>106.6279</v>
       </c>
       <c r="D101" s="2" t="n">
         <v>0.0159</v>
@@ -2178,10 +2178,10 @@
         <v>600</v>
       </c>
       <c r="B102" s="2" t="n">
-        <v>10.1606</v>
+        <v>10.1603</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>111.9334</v>
+        <v>111.9447</v>
       </c>
       <c r="D102" s="2" t="n">
         <v>0.0158</v>
@@ -2195,10 +2195,10 @@
         <v>602</v>
       </c>
       <c r="B103" s="2" t="n">
-        <v>10.0526</v>
+        <v>10.0524</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>117.2592</v>
+        <v>117.2688</v>
       </c>
       <c r="D103" s="2" t="n">
         <v>0.0157</v>
@@ -2212,10 +2212,10 @@
         <v>604</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>9.967700000000001</v>
+        <v>9.967599999999999</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>122.5244</v>
+        <v>122.5327</v>
       </c>
       <c r="D104" s="2" t="n">
         <v>0.0157</v>
@@ -2229,10 +2229,10 @@
         <v>606</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>9.8904</v>
+        <v>9.8902</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>127.5718</v>
+        <v>127.5789</v>
       </c>
       <c r="D105" s="2" t="n">
         <v>0.0156</v>
@@ -2246,10 +2246,10 @@
         <v>608</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>9.837400000000001</v>
+        <v>9.837300000000001</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>132.6233</v>
+        <v>132.6293</v>
       </c>
       <c r="D106" s="2" t="n">
         <v>0.0156</v>
@@ -2266,7 +2266,7 @@
         <v>9.775</v>
       </c>
       <c r="C107" s="2" t="n">
-        <v>137.6438</v>
+        <v>137.649</v>
       </c>
       <c r="D107" s="2" t="n">
         <v>0.0155</v>
@@ -2280,10 +2280,10 @@
         <v>612</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>9.7239</v>
+        <v>9.723800000000001</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>142.44</v>
+        <v>142.4444</v>
       </c>
       <c r="D108" s="2" t="n">
         <v>0.0155</v>
@@ -2300,7 +2300,7 @@
         <v>9.6584</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>147.5353</v>
+        <v>147.539</v>
       </c>
       <c r="D109" s="2" t="n">
         <v>0.0154</v>
@@ -2314,10 +2314,10 @@
         <v>616</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>9.648</v>
+        <v>9.6479</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>152.2697</v>
+        <v>152.2727</v>
       </c>
       <c r="D110" s="2" t="n">
         <v>0.0154</v>
@@ -2331,10 +2331,10 @@
         <v>618</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>9.622199999999999</v>
+        <v>9.6221</v>
       </c>
       <c r="C111" s="2" t="n">
-        <v>156.9023</v>
+        <v>156.9047</v>
       </c>
       <c r="D111" s="2" t="n">
         <v>0.0153</v>
@@ -2348,10 +2348,10 @@
         <v>620</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>9.582000000000001</v>
+        <v>9.581899999999999</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>161.5666</v>
+        <v>161.5685</v>
       </c>
       <c r="D112" s="2" t="n">
         <v>0.0153</v>
@@ -2368,7 +2368,7 @@
         <v>9.5769</v>
       </c>
       <c r="C113" s="2" t="n">
-        <v>166.2844</v>
+        <v>166.2858</v>
       </c>
       <c r="D113" s="2" t="n">
         <v>0.0153</v>
@@ -2385,7 +2385,7 @@
         <v>9.545</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>171.1446</v>
+        <v>171.1456</v>
       </c>
       <c r="D114" s="2" t="n">
         <v>0.0152</v>
@@ -2402,7 +2402,7 @@
         <v>9.5259</v>
       </c>
       <c r="C115" s="2" t="n">
-        <v>175.6089</v>
+        <v>175.6094</v>
       </c>
       <c r="D115" s="2" t="n">
         <v>0.0152</v>
@@ -2419,7 +2419,7 @@
         <v>9.5184</v>
       </c>
       <c r="C116" s="2" t="n">
-        <v>180.243</v>
+        <v>180.2431</v>
       </c>
       <c r="D116" s="2" t="n">
         <v>0.0152</v>
@@ -2436,7 +2436,7 @@
         <v>9.520099999999999</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>184.5581</v>
+        <v>184.5578</v>
       </c>
       <c r="D117" s="2" t="n">
         <v>0.0151</v>
@@ -2453,7 +2453,7 @@
         <v>9.4975</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>189.186</v>
+        <v>189.1853</v>
       </c>
       <c r="D118" s="2" t="n">
         <v>0.0151</v>
@@ -2470,7 +2470,7 @@
         <v>9.4976</v>
       </c>
       <c r="C119" s="2" t="n">
-        <v>193.5678</v>
+        <v>193.5667</v>
       </c>
       <c r="D119" s="2" t="n">
         <v>0.0151</v>
@@ -2487,7 +2487,7 @@
         <v>9.5116</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>198.2421</v>
+        <v>198.2406</v>
       </c>
       <c r="D120" s="2" t="n">
         <v>0.0151</v>
@@ -2504,7 +2504,7 @@
         <v>9.5069</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>202.513</v>
+        <v>202.5111</v>
       </c>
       <c r="D121" s="2" t="n">
         <v>0.015</v>
@@ -2521,7 +2521,7 @@
         <v>9.488099999999999</v>
       </c>
       <c r="C122" s="2" t="n">
-        <v>206.9513</v>
+        <v>206.949</v>
       </c>
       <c r="D122" s="2" t="n">
         <v>0.015</v>
@@ -2538,7 +2538,7 @@
         <v>9.536899999999999</v>
       </c>
       <c r="C123" s="2" t="n">
-        <v>211.4403</v>
+        <v>211.4376</v>
       </c>
       <c r="D123" s="2" t="n">
         <v>0.015</v>
@@ -2552,10 +2552,10 @@
         <v>644</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>9.5566</v>
+        <v>9.5565</v>
       </c>
       <c r="C124" s="2" t="n">
-        <v>215.9806</v>
+        <v>215.9775</v>
       </c>
       <c r="D124" s="2" t="n">
         <v>0.015</v>
@@ -2572,7 +2572,7 @@
         <v>9.5901</v>
       </c>
       <c r="C125" s="2" t="n">
-        <v>220.1894</v>
+        <v>220.1858</v>
       </c>
       <c r="D125" s="2" t="n">
         <v>0.015</v>
@@ -2586,10 +2586,10 @@
         <v>648</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>9.6235</v>
+        <v>9.6234</v>
       </c>
       <c r="C126" s="2" t="n">
-        <v>224.5525</v>
+        <v>224.5484</v>
       </c>
       <c r="D126" s="2" t="n">
         <v>0.015</v>
@@ -2603,10 +2603,10 @@
         <v>650</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>9.678000000000001</v>
+        <v>9.677899999999999</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>229.1828</v>
+        <v>229.1782</v>
       </c>
       <c r="D127" s="2" t="n">
         <v>0.015</v>
@@ -2620,10 +2620,10 @@
         <v>652</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>9.7323</v>
+        <v>9.732200000000001</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>233.3985</v>
+        <v>233.3934</v>
       </c>
       <c r="D128" s="2" t="n">
         <v>0.015</v>
@@ -2637,10 +2637,10 @@
         <v>654</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>9.8003</v>
+        <v>9.8001</v>
       </c>
       <c r="C129" s="2" t="n">
-        <v>237.9385</v>
+        <v>237.9328</v>
       </c>
       <c r="D129" s="2" t="n">
         <v>0.015</v>
@@ -2654,10 +2654,10 @@
         <v>656</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>9.863</v>
+        <v>9.8629</v>
       </c>
       <c r="C130" s="2" t="n">
-        <v>242.4851</v>
+        <v>242.4789</v>
       </c>
       <c r="D130" s="2" t="n">
         <v>0.015</v>
@@ -2671,10 +2671,10 @@
         <v>658</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>9.9488</v>
+        <v>9.948600000000001</v>
       </c>
       <c r="C131" s="2" t="n">
-        <v>246.5312</v>
+        <v>246.5243</v>
       </c>
       <c r="D131" s="2" t="n">
         <v>0.015</v>
@@ -2688,10 +2688,10 @@
         <v>660</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>10.0588</v>
+        <v>10.0585</v>
       </c>
       <c r="C132" s="2" t="n">
-        <v>250.9625</v>
+        <v>250.9549</v>
       </c>
       <c r="D132" s="2" t="n">
         <v>0.015</v>
@@ -2705,10 +2705,10 @@
         <v>662</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>10.1818</v>
+        <v>10.1815</v>
       </c>
       <c r="C133" s="2" t="n">
-        <v>255.5643</v>
+        <v>255.5559</v>
       </c>
       <c r="D133" s="2" t="n">
         <v>0.015</v>
@@ -2722,10 +2722,10 @@
         <v>664</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>10.3116</v>
+        <v>10.3112</v>
       </c>
       <c r="C134" s="2" t="n">
-        <v>259.9957</v>
+        <v>259.9865</v>
       </c>
       <c r="D134" s="2" t="n">
         <v>0.015</v>
@@ -2739,10 +2739,10 @@
         <v>666</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>10.445</v>
+        <v>10.4446</v>
       </c>
       <c r="C135" s="2" t="n">
-        <v>264.5506</v>
+        <v>264.5406</v>
       </c>
       <c r="D135" s="2" t="n">
         <v>0.015</v>
@@ -2756,10 +2756,10 @@
         <v>668</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>10.6189</v>
+        <v>10.6184</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>269.0513</v>
+        <v>269.0403</v>
       </c>
       <c r="D136" s="2" t="n">
         <v>0.015</v>
@@ -2773,10 +2773,10 @@
         <v>670</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>10.8115</v>
+        <v>10.8109</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>273.6486</v>
+        <v>273.6366</v>
       </c>
       <c r="D137" s="2" t="n">
         <v>0.015</v>
@@ -2790,10 +2790,10 @@
         <v>672</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>11.0087</v>
+        <v>11.008</v>
       </c>
       <c r="C138" s="2" t="n">
-        <v>278.3005</v>
+        <v>278.2875</v>
       </c>
       <c r="D138" s="2" t="n">
         <v>0.015</v>
@@ -2807,10 +2807,10 @@
         <v>674</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>11.2724</v>
+        <v>11.2716</v>
       </c>
       <c r="C139" s="2" t="n">
-        <v>283.0413</v>
+        <v>283.0272</v>
       </c>
       <c r="D139" s="2" t="n">
         <v>0.015</v>
@@ -2824,10 +2824,10 @@
         <v>676</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>11.5066</v>
+        <v>11.5058</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>288.0126</v>
+        <v>287.9974</v>
       </c>
       <c r="D140" s="2" t="n">
         <v>0.015</v>
@@ -2841,10 +2841,10 @@
         <v>678</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>11.7508</v>
+        <v>11.7499</v>
       </c>
       <c r="C141" s="2" t="n">
-        <v>293.0698</v>
+        <v>293.0536</v>
       </c>
       <c r="D141" s="2" t="n">
         <v>0.015</v>
@@ -2858,10 +2858,10 @@
         <v>680</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>12.1026</v>
+        <v>12.1016</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>298.1392</v>
+        <v>298.1221</v>
       </c>
       <c r="D142" s="2" t="n">
         <v>0.015</v>
@@ -2875,10 +2875,10 @@
         <v>682</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>12.4017</v>
+        <v>12.4006</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>303.4108</v>
+        <v>303.3928</v>
       </c>
       <c r="D143" s="2" t="n">
         <v>0.015</v>
@@ -2892,10 +2892,10 @@
         <v>684</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>12.733</v>
+        <v>12.7319</v>
       </c>
       <c r="C144" s="2" t="n">
-        <v>308.9145</v>
+        <v>308.896</v>
       </c>
       <c r="D144" s="2" t="n">
         <v>0.015</v>
@@ -2909,10 +2909,10 @@
         <v>686</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>13.0653</v>
+        <v>13.0644</v>
       </c>
       <c r="C145" s="2" t="n">
-        <v>314.5531</v>
+        <v>314.5344</v>
       </c>
       <c r="D145" s="2" t="n">
         <v>0.015</v>
@@ -2926,10 +2926,10 @@
         <v>688</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>13.4069</v>
+        <v>13.4061</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>320.3325</v>
+        <v>320.3142</v>
       </c>
       <c r="D146" s="2" t="n">
         <v>0.015</v>
@@ -2943,10 +2943,10 @@
         <v>690</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>13.6791</v>
+        <v>13.6784</v>
       </c>
       <c r="C147" s="2" t="n">
-        <v>326.567</v>
+        <v>326.5499</v>
       </c>
       <c r="D147" s="2" t="n">
         <v>0.015</v>
@@ -2960,10 +2960,10 @@
         <v>692</v>
       </c>
       <c r="B148" s="2" t="n">
-        <v>13.9661</v>
+        <v>13.9657</v>
       </c>
       <c r="C148" s="2" t="n">
-        <v>332.6931</v>
+        <v>332.6778</v>
       </c>
       <c r="D148" s="2" t="n">
         <v>0.015</v>
@@ -2977,10 +2977,10 @@
         <v>694</v>
       </c>
       <c r="B149" s="2" t="n">
-        <v>14.2259</v>
+        <v>14.2258</v>
       </c>
       <c r="C149" s="2" t="n">
-        <v>339.2666</v>
+        <v>339.2541</v>
       </c>
       <c r="D149" s="2" t="n">
         <v>0.015</v>
@@ -2994,10 +2994,10 @@
         <v>696</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>14.377</v>
+        <v>14.3772</v>
       </c>
       <c r="C150" s="2" t="n">
-        <v>345.6659</v>
+        <v>345.657</v>
       </c>
       <c r="D150" s="2" t="n">
         <v>0.015</v>
@@ -3011,10 +3011,10 @@
         <v>698</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>14.5176</v>
+        <v>14.5179</v>
       </c>
       <c r="C151" s="2" t="n">
-        <v>352.4344</v>
+        <v>352.4295</v>
       </c>
       <c r="D151" s="2" t="n">
         <v>0.015</v>
@@ -3028,10 +3028,10 @@
         <v>700</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>14.5963</v>
+        <v>14.5967</v>
       </c>
       <c r="C152" s="2" t="n">
-        <v>359.1066</v>
+        <v>359.1061</v>
       </c>
       <c r="D152" s="2" t="n">
         <v>0.015</v>
@@ -3045,10 +3045,10 @@
         <v>702</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>14.5149</v>
+        <v>14.5153</v>
       </c>
       <c r="C153" s="2" t="n">
-        <v>5.7578</v>
+        <v>5.7616</v>
       </c>
       <c r="D153" s="2" t="n">
         <v>0.015</v>
@@ -3062,10 +3062,10 @@
         <v>704</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>14.4495</v>
+        <v>14.4497</v>
       </c>
       <c r="C154" s="2" t="n">
-        <v>12.3102</v>
+        <v>12.3179</v>
       </c>
       <c r="D154" s="2" t="n">
         <v>0.015</v>
@@ -3082,7 +3082,7 @@
         <v>14.2563</v>
       </c>
       <c r="C155" s="2" t="n">
-        <v>18.8236</v>
+        <v>18.8343</v>
       </c>
       <c r="D155" s="2" t="n">
         <v>0.015</v>
@@ -3096,10 +3096,10 @@
         <v>708</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>14.0808</v>
+        <v>14.0806</v>
       </c>
       <c r="C156" s="2" t="n">
-        <v>24.8166</v>
+        <v>24.8297</v>
       </c>
       <c r="D156" s="2" t="n">
         <v>0.015</v>
@@ -3113,10 +3113,10 @@
         <v>710</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>13.8383</v>
+        <v>13.8378</v>
       </c>
       <c r="C157" s="2" t="n">
-        <v>30.9249</v>
+        <v>30.9396</v>
       </c>
       <c r="D157" s="2" t="n">
         <v>0.015</v>
@@ -3130,10 +3130,10 @@
         <v>712</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>13.5574</v>
+        <v>13.5568</v>
       </c>
       <c r="C158" s="2" t="n">
-        <v>36.4979</v>
+        <v>36.5133</v>
       </c>
       <c r="D158" s="2" t="n">
         <v>0.015</v>
@@ -3147,16 +3147,16 @@
         <v>714</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>13.2666</v>
+        <v>13.2659</v>
       </c>
       <c r="C159" s="2" t="n">
-        <v>41.9928</v>
+        <v>42.0084</v>
       </c>
       <c r="D159" s="2" t="n">
         <v>0.015</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>0.07389999999999999</v>
+        <v>0.074</v>
       </c>
     </row>
     <row r="160">
@@ -3164,10 +3164,10 @@
         <v>716</v>
       </c>
       <c r="B160" s="2" t="n">
-        <v>12.9301</v>
+        <v>12.9293</v>
       </c>
       <c r="C160" s="2" t="n">
-        <v>47.2638</v>
+        <v>47.2792</v>
       </c>
       <c r="D160" s="2" t="n">
         <v>0.015</v>
@@ -3181,10 +3181,10 @@
         <v>718</v>
       </c>
       <c r="B161" s="2" t="n">
-        <v>12.679</v>
+        <v>12.6782</v>
       </c>
       <c r="C161" s="2" t="n">
-        <v>52.1177</v>
+        <v>52.1325</v>
       </c>
       <c r="D161" s="2" t="n">
         <v>0.015</v>
@@ -3198,10 +3198,10 @@
         <v>720</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>12.3961</v>
+        <v>12.3953</v>
       </c>
       <c r="C162" s="2" t="n">
-        <v>56.9072</v>
+        <v>56.9212</v>
       </c>
       <c r="D162" s="2" t="n">
         <v>0.015</v>
@@ -3215,10 +3215,10 @@
         <v>722</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>12.1117</v>
+        <v>12.111</v>
       </c>
       <c r="C163" s="2" t="n">
-        <v>61.6168</v>
+        <v>61.6299</v>
       </c>
       <c r="D163" s="2" t="n">
         <v>0.015</v>
@@ -3232,10 +3232,10 @@
         <v>724</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>11.8365</v>
+        <v>11.8358</v>
       </c>
       <c r="C164" s="2" t="n">
-        <v>65.88039999999999</v>
+        <v>65.8926</v>
       </c>
       <c r="D164" s="2" t="n">
         <v>0.015</v>
@@ -3249,10 +3249,10 @@
         <v>726</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>11.6076</v>
+        <v>11.6069</v>
       </c>
       <c r="C165" s="2" t="n">
-        <v>70.25790000000001</v>
+        <v>70.26909999999999</v>
       </c>
       <c r="D165" s="2" t="n">
         <v>0.015</v>
@@ -3266,10 +3266,10 @@
         <v>728</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>11.3809</v>
+        <v>11.3803</v>
       </c>
       <c r="C166" s="2" t="n">
-        <v>74.4503</v>
+        <v>74.4607</v>
       </c>
       <c r="D166" s="2" t="n">
         <v>0.015</v>
@@ -3283,10 +3283,10 @@
         <v>730</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>11.1694</v>
+        <v>11.1688</v>
       </c>
       <c r="C167" s="2" t="n">
-        <v>78.21259999999999</v>
+        <v>78.2221</v>
       </c>
       <c r="D167" s="2" t="n">
         <v>0.015</v>
@@ -3300,10 +3300,10 @@
         <v>732</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>10.9529</v>
+        <v>10.9524</v>
       </c>
       <c r="C168" s="2" t="n">
-        <v>82.1906</v>
+        <v>82.1992</v>
       </c>
       <c r="D168" s="2" t="n">
         <v>0.015</v>
@@ -3317,10 +3317,10 @@
         <v>734</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>10.7579</v>
+        <v>10.7575</v>
       </c>
       <c r="C169" s="2" t="n">
-        <v>85.86490000000001</v>
+        <v>85.8728</v>
       </c>
       <c r="D169" s="2" t="n">
         <v>0.015</v>
@@ -3334,10 +3334,10 @@
         <v>736</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>10.5936</v>
+        <v>10.5932</v>
       </c>
       <c r="C170" s="2" t="n">
-        <v>89.51860000000001</v>
+        <v>89.5258</v>
       </c>
       <c r="D170" s="2" t="n">
         <v>0.015</v>
@@ -3351,10 +3351,10 @@
         <v>738</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>10.4809</v>
+        <v>10.4806</v>
       </c>
       <c r="C171" s="2" t="n">
-        <v>93.1373</v>
+        <v>93.1439</v>
       </c>
       <c r="D171" s="2" t="n">
         <v>0.015</v>
@@ -3368,10 +3368,10 @@
         <v>740</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>10.3072</v>
+        <v>10.307</v>
       </c>
       <c r="C172" s="2" t="n">
-        <v>96.7323</v>
+        <v>96.7383</v>
       </c>
       <c r="D172" s="2" t="n">
         <v>0.015</v>
@@ -3385,10 +3385,10 @@
         <v>742</v>
       </c>
       <c r="B173" s="2" t="n">
-        <v>10.1984</v>
+        <v>10.1982</v>
       </c>
       <c r="C173" s="2" t="n">
-        <v>99.8695</v>
+        <v>99.875</v>
       </c>
       <c r="D173" s="2" t="n">
         <v>0.015</v>
@@ -3402,10 +3402,10 @@
         <v>744</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>10.0702</v>
+        <v>10.07</v>
       </c>
       <c r="C174" s="2" t="n">
-        <v>103.4294</v>
+        <v>103.4344</v>
       </c>
       <c r="D174" s="2" t="n">
         <v>0.015</v>
@@ -3419,10 +3419,10 @@
         <v>746</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>9.954700000000001</v>
+        <v>9.954499999999999</v>
       </c>
       <c r="C175" s="2" t="n">
-        <v>106.8545</v>
+        <v>106.8591</v>
       </c>
       <c r="D175" s="2" t="n">
         <v>0.015</v>
@@ -3436,10 +3436,10 @@
         <v>748</v>
       </c>
       <c r="B176" s="2" t="n">
-        <v>9.860799999999999</v>
+        <v>9.8606</v>
       </c>
       <c r="C176" s="2" t="n">
-        <v>110.0109</v>
+        <v>110.0151</v>
       </c>
       <c r="D176" s="2" t="n">
         <v>0.015</v>
@@ -3453,10 +3453,10 @@
         <v>750</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>9.789199999999999</v>
+        <v>9.789</v>
       </c>
       <c r="C177" s="2" t="n">
-        <v>113.4265</v>
+        <v>113.4303</v>
       </c>
       <c r="D177" s="2" t="n">
         <v>0.015</v>
@@ -3470,10 +3470,10 @@
         <v>752</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>9.674099999999999</v>
+        <v>9.673999999999999</v>
       </c>
       <c r="C178" s="2" t="n">
-        <v>116.6691</v>
+        <v>116.6726</v>
       </c>
       <c r="D178" s="2" t="n">
         <v>0.015</v>
@@ -3487,10 +3487,10 @@
         <v>754</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>9.612399999999999</v>
+        <v>9.612299999999999</v>
       </c>
       <c r="C179" s="2" t="n">
-        <v>119.8543</v>
+        <v>119.8576</v>
       </c>
       <c r="D179" s="2" t="n">
         <v>0.015</v>
@@ -3504,10 +3504,10 @@
         <v>756</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>9.5162</v>
+        <v>9.5161</v>
       </c>
       <c r="C180" s="2" t="n">
-        <v>123.0946</v>
+        <v>123.0976</v>
       </c>
       <c r="D180" s="2" t="n">
         <v>0.015</v>
@@ -3521,10 +3521,10 @@
         <v>758</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>9.4467</v>
+        <v>9.4466</v>
       </c>
       <c r="C181" s="2" t="n">
-        <v>126.178</v>
+        <v>126.1807</v>
       </c>
       <c r="D181" s="2" t="n">
         <v>0.015</v>
@@ -3541,7 +3541,7 @@
         <v>9.388</v>
       </c>
       <c r="C182" s="2" t="n">
-        <v>129.2439</v>
+        <v>129.2463</v>
       </c>
       <c r="D182" s="2" t="n">
         <v>0.015</v>
@@ -3558,7 +3558,7 @@
         <v>9.3361</v>
       </c>
       <c r="C183" s="2" t="n">
-        <v>132.2989</v>
+        <v>132.3011</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>0.015</v>
@@ -3575,7 +3575,7 @@
         <v>9.2913</v>
       </c>
       <c r="C184" s="2" t="n">
-        <v>135.6134</v>
+        <v>135.6154</v>
       </c>
       <c r="D184" s="2" t="n">
         <v>0.015</v>
@@ -3589,10 +3589,10 @@
         <v>766</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>9.250999999999999</v>
+        <v>9.2509</v>
       </c>
       <c r="C185" s="2" t="n">
-        <v>138.7809</v>
+        <v>138.7828</v>
       </c>
       <c r="D185" s="2" t="n">
         <v>0.015</v>
@@ -3609,7 +3609,7 @@
         <v>9.215999999999999</v>
       </c>
       <c r="C186" s="2" t="n">
-        <v>141.5861</v>
+        <v>141.5878</v>
       </c>
       <c r="D186" s="2" t="n">
         <v>0.015</v>
@@ -3626,7 +3626,7 @@
         <v>9.1602</v>
       </c>
       <c r="C187" s="2" t="n">
-        <v>144.7935</v>
+        <v>144.795</v>
       </c>
       <c r="D187" s="2" t="n">
         <v>0.015</v>
@@ -3643,7 +3643,7 @@
         <v>9.1126</v>
       </c>
       <c r="C188" s="2" t="n">
-        <v>147.6566</v>
+        <v>147.658</v>
       </c>
       <c r="D188" s="2" t="n">
         <v>0.015</v>
@@ -3660,7 +3660,7 @@
         <v>9.080500000000001</v>
       </c>
       <c r="C189" s="2" t="n">
-        <v>150.6904</v>
+        <v>150.6916</v>
       </c>
       <c r="D189" s="2" t="n">
         <v>0.015</v>
@@ -3677,7 +3677,7 @@
         <v>9.063700000000001</v>
       </c>
       <c r="C190" s="2" t="n">
-        <v>153.635</v>
+        <v>153.636</v>
       </c>
       <c r="D190" s="2" t="n">
         <v>0.015</v>
@@ -3694,7 +3694,7 @@
         <v>9.055999999999999</v>
       </c>
       <c r="C191" s="2" t="n">
-        <v>156.4736</v>
+        <v>156.4746</v>
       </c>
       <c r="D191" s="2" t="n">
         <v>0.015</v>
@@ -3711,7 +3711,7 @@
         <v>9.0229</v>
       </c>
       <c r="C192" s="2" t="n">
-        <v>159.5681</v>
+        <v>159.5689</v>
       </c>
       <c r="D192" s="2" t="n">
         <v>0.015</v>
@@ -3728,7 +3728,7 @@
         <v>9.0036</v>
       </c>
       <c r="C193" s="2" t="n">
-        <v>162.3053</v>
+        <v>162.306</v>
       </c>
       <c r="D193" s="2" t="n">
         <v>0.015</v>
@@ -3745,7 +3745,7 @@
         <v>8.9933</v>
       </c>
       <c r="C194" s="2" t="n">
-        <v>165.304</v>
+        <v>165.3045</v>
       </c>
       <c r="D194" s="2" t="n">
         <v>0.015</v>
@@ -3762,7 +3762,7 @@
         <v>8.9589</v>
       </c>
       <c r="C195" s="2" t="n">
-        <v>168.094</v>
+        <v>168.0944</v>
       </c>
       <c r="D195" s="2" t="n">
         <v>0.015</v>
@@ -3779,7 +3779,7 @@
         <v>8.9565</v>
       </c>
       <c r="C196" s="2" t="n">
-        <v>171.0033</v>
+        <v>171.0037</v>
       </c>
       <c r="D196" s="2" t="n">
         <v>0.015</v>
@@ -3796,7 +3796,7 @@
         <v>8.943099999999999</v>
       </c>
       <c r="C197" s="2" t="n">
-        <v>173.8544</v>
+        <v>173.8547</v>
       </c>
       <c r="D197" s="2" t="n">
         <v>0.015</v>
@@ -3813,7 +3813,7 @@
         <v>8.9209</v>
       </c>
       <c r="C198" s="2" t="n">
-        <v>176.7495</v>
+        <v>176.7497</v>
       </c>
       <c r="D198" s="2" t="n">
         <v>0.015</v>
@@ -3830,7 +3830,7 @@
         <v>8.9093</v>
       </c>
       <c r="C199" s="2" t="n">
-        <v>179.6004</v>
+        <v>179.6005</v>
       </c>
       <c r="D199" s="2" t="n">
         <v>0.015</v>
@@ -3864,7 +3864,7 @@
         <v>8.946199999999999</v>
       </c>
       <c r="C201" s="2" t="n">
-        <v>185.4123</v>
+        <v>185.4122</v>
       </c>
       <c r="D201" s="2" t="n">
         <v>0.015</v>
@@ -3881,7 +3881,7 @@
         <v>8.9068</v>
       </c>
       <c r="C202" s="2" t="n">
-        <v>188.2478</v>
+        <v>188.2476</v>
       </c>
       <c r="D202" s="2" t="n">
         <v>0.015</v>
